--- a/Figure 2/Figure 2-F.xlsx
+++ b/Figure 2/Figure 2-F.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417245A6-9A41-455C-973A-B9217542EB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC4249B-B606-4609-922B-3D3E7E927BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24380" yWindow="1850" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +168,12 @@
       <name val="等线"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -189,13 +195,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -482,353 +489,354 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.4140625" style="1" customWidth="1"/>
-    <col min="2" max="4" width="8.6640625" style="3"/>
+    <col min="2" max="4" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>234.86913143333337</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>310.31376</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>0.75687630299999997</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>280.17240720720702</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>322.30129279279242</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>0.8692872584514576</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>238.80383333333302</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>310.32942222222181</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="4">
         <v>0.76951721697316056</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>283.49548055555528</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>350.65300277777743</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="4">
         <v>0.80847869064226285</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>244.88693409090885</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>324.40045378787846</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="4">
         <v>0.75489084935447537</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>261.92079689922446</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>313.15636821705397</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="4">
         <v>0.83638981506415588</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>299.81512058823506</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>315.90209999999968</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="4">
         <v>0.949076060552416</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>277.2740095238093</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>312.47482857142819</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="4">
         <v>0.88734830511452734</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>270.93895111111084</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>290.26774999999969</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="4">
         <v>0.93341044987295729</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="4">
         <v>222.67167555555537</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="4">
         <v>304.34868888888866</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="4">
         <v>0.73163343127411384</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="4">
         <v>211.93730317460296</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="4">
         <v>209.92450317460299</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="4">
         <v>1.0095882089492232</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="4">
         <v>229.09831886792432</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="4">
         <v>224.94276540880483</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="4">
         <v>1.0184738257821597</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>297.55220133333302</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>289.65522799999968</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="4">
         <v>1.0272633550854928</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>288.17437514124248</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>323.98598022598821</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="4">
         <v>0.8894655717516966</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>254.19935204678333</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>316.5064432748535</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="4">
         <v>0.80314116015021275</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>227.33223758865228</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>299.78353262411321</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="4">
         <v>0.75832129803372239</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>190.86908333333315</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="4">
         <v>243.02385555555531</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="4">
         <v>0.78539237597479572</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>256.6001447368418</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>299.60018859649085</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="4">
         <v>0.85647524435452671</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>288.29233137254869</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="4">
         <v>254.0562852941174</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="4">
         <v>1.1347577212616358</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>253.2153132075469</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>295.39817106918213</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="4">
         <v>0.85720000327369661</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>286.26915061728374</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>278.67022839506137</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="4">
         <v>1.0272685111215023</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="4">
         <v>284.84226315789437</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="4">
         <v>281.86750935672495</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="4">
         <v>1.0105537307508707</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="4">
         <v>293.2433607142853</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="4">
         <v>293.88556785714258</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="4">
         <v>0.99781477141752872</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="4">
         <v>294.13098873873849</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="4">
         <v>284.95763243243215</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="4">
         <v>1.032192000712532</v>
       </c>
     </row>
